--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -517,6 +517,9 @@
       <c r="A11" t="str">
         <v>2</v>
       </c>
+      <c r="C11" t="str">
+        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05555510151020</v>
+        <v>05555510151029</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,89 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3</v>
+      </c>
+      <c r="C15" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F16" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>5_绿洋桔梗_Light Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F18" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>254_梦幻海葵_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05555510151029</v>
+        <v>055555101510292151010353550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>254_梦幻海葵_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055555101510292151010353550</v>
+        <v>055555101510292151010353555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>608_康乃馨笑颜_undefined_undefined_20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>495_大飞燕深粉色_delphinium pink_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>402_大飞燕深紫色_delphinium purple_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +744,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055555101510292151010353555</v>
+        <v>05555510151029215101035355589155555550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -686,6 +686,9 @@
       <c r="C31" t="str">
         <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
       </c>
+      <c r="F31" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -744,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05555510151029215101035355589155555550</v>
+        <v>055555101510292151010353555891555555520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -690,9 +690,47 @@
         <v>20</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F32" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>432_小刺秦/情人果_small Eryngium_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>5</v>
+      </c>
+      <c r="C34" t="str">
+        <v>432_小刺秦/情人果_small Eryngium_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>6</v>
+      </c>
+      <c r="C35" t="str">
+        <v>504_大花葱_Allium _undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L35"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -747,7 +785,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055555101510292151010353555891555555520</v>
+        <v>055555101510292151010353555891555555520157815</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,15 +443,18 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
       </c>
       <c r="F2" t="str">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
       <c r="C3" t="str">
-        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+        <v>388_大丽花_dahlia_undefined_1bunch</v>
       </c>
       <c r="F3" t="str">
         <v>5</v>
@@ -459,7 +462,7 @@
     </row>
     <row r="4">
       <c r="C4" t="str">
-        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
       </c>
       <c r="F4" t="str">
         <v>5</v>
@@ -467,7 +470,7 @@
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
       </c>
       <c r="F5" t="str">
         <v>5</v>
@@ -475,15 +478,18 @@
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+        <v>655_大丽花 莎拉_undefined_undefined_5stems</v>
       </c>
       <c r="F6" t="str">
         <v>5</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="str">
+        <v>3</v>
+      </c>
       <c r="C7" t="str">
-        <v>771_美洲茶_undefined_undefined_1bunch</v>
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
       </c>
       <c r="F7" t="str">
         <v>10</v>
@@ -491,85 +497,85 @@
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>770_弯葱_undefined_undefined_10stems</v>
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
       </c>
       <c r="F8" t="str">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="str">
+        <v>4</v>
+      </c>
       <c r="C9" t="str">
-        <v>788_直葱_undefined_undefined_1bunch</v>
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F9" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="str">
-        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F10" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>2</v>
-      </c>
       <c r="C11" t="str">
-        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" t="str">
-        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
       </c>
       <c r="F12" t="str">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="str">
-        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F13" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="str">
+        <v>5</v>
+      </c>
       <c r="C14" t="str">
-        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F14" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>3</v>
-      </c>
       <c r="C15" t="str">
-        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F15" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="C16" t="str">
-        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F16" t="str">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" t="str">
-        <v>5_绿洋桔梗_Light Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F17" t="str">
         <v>5</v>
@@ -577,23 +583,23 @@
     </row>
     <row r="18">
       <c r="C18" t="str">
-        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F18" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="str">
-        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F19" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" t="str">
-        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F20" t="str">
         <v>5</v>
@@ -601,50 +607,50 @@
     </row>
     <row r="21">
       <c r="C21" t="str">
-        <v>254_梦幻海葵_undefined_Rosa rugosa Thunb._10stems</v>
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F21" t="str">
         <v>5</v>
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="str">
+        <v>6</v>
+      </c>
       <c r="C22" t="str">
-        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F22" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" t="str">
-        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F23" t="str">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" t="str">
-        <v>608_康乃馨笑颜_undefined_undefined_20stems</v>
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F24" t="str">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>4</v>
-      </c>
       <c r="C25" t="str">
-        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F25" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" t="str">
-        <v>495_大飞燕深粉色_delphinium pink_undefined_1bunch</v>
+        <v>226_梦幻芭比_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F26" t="str">
         <v>5</v>
@@ -652,7 +658,7 @@
     </row>
     <row r="27">
       <c r="C27" t="str">
-        <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
+        <v>595_玉兰叶_undefined_undefined_1bunch</v>
       </c>
       <c r="F27" t="str">
         <v>5</v>
@@ -660,77 +666,42 @@
     </row>
     <row r="28">
       <c r="C28" t="str">
-        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
       </c>
       <c r="F28" t="str">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="C29" t="str">
-        <v>402_大飞燕深紫色_delphinium purple_undefined_1bunch</v>
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
       </c>
       <c r="F29" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" t="str">
-        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
       </c>
       <c r="F30" t="str">
         <v>5</v>
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="str">
+        <v>6</v>
+      </c>
       <c r="C31" t="str">
-        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
       </c>
       <c r="F31" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="str">
-        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
-      </c>
-      <c r="F32" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="str">
-        <v>432_小刺秦/情人果_small Eryngium_undefined_1bunch</v>
-      </c>
-      <c r="F33" t="str">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>5</v>
-      </c>
-      <c r="C34" t="str">
-        <v>432_小刺秦/情人果_small Eryngium_undefined_1bunch</v>
-      </c>
-      <c r="F34" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>6</v>
-      </c>
-      <c r="C35" t="str">
-        <v>504_大花葱_Allium _undefined_1bunch</v>
-      </c>
-      <c r="F35" t="str">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -785,7 +756,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055555101510292151010353555891555555520157815</v>
+        <v>020055551020131055105510563557561055151053</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-19.xlsx
@@ -758,6 +758,9 @@
       <c r="G2" t="str">
         <v>020055551020131055105510563557561055151053</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
